--- a/API/CreateData/yizhi.xlsx
+++ b/API/CreateData/yizhi.xlsx
@@ -1342,7 +1342,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W6"/>
+  <dimension ref="A1:W18"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="15" outlineLevelRow="1"/>
   <cols>
     <col width="35.9166666666667" customWidth="1" style="1" min="1" max="1"/>
@@ -1486,256 +1486,1024 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>XG2024013015562113652147212</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
+      <c r="A3" s="0" t="inlineStr">
+        <is>
+          <t>XG2024051416323915594083772</t>
+        </is>
+      </c>
+      <c r="B3" s="0" t="inlineStr">
         <is>
           <t>新贵测试</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C3" s="0" t="inlineStr">
         <is>
           <t>86</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>13652147212</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr">
+      <c r="D3" s="0" t="inlineStr">
+        <is>
+          <t>15594083772</t>
+        </is>
+      </c>
+      <c r="E3" s="0" t="inlineStr"/>
+      <c r="F3" s="0" t="inlineStr">
         <is>
           <t>468078</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>10025667</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>0.03</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>2024-01-30 15:56:21</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
+      <c r="G3" s="0" t="inlineStr">
+        <is>
+          <t>10025804</t>
+        </is>
+      </c>
+      <c r="H3" s="0" t="inlineStr">
+        <is>
+          <t>2.3</t>
+        </is>
+      </c>
+      <c r="I3" s="0" t="inlineStr">
+        <is>
+          <t>2024-05-14 16:32:39</t>
+        </is>
+      </c>
+      <c r="J3" s="0" t="inlineStr">
         <is>
           <t>第三方售卖</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="K3" s="0" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="L3" s="0" t="inlineStr">
         <is>
           <t>1999</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr"/>
-      <c r="O3" t="inlineStr">
+      <c r="M3" s="0" t="inlineStr"/>
+      <c r="O3" s="0" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>XG2024013015562113652147213</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
+      <c r="A4" s="0" t="inlineStr">
+        <is>
+          <t>XG2024050915373013652124126</t>
+        </is>
+      </c>
+      <c r="B4" s="0" t="inlineStr">
         <is>
           <t>新贵测试</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C4" s="0" t="inlineStr">
         <is>
           <t>86</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>13652147213</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr">
+      <c r="D4" s="0" t="inlineStr">
+        <is>
+          <t>13652124126</t>
+        </is>
+      </c>
+      <c r="E4" s="0" t="inlineStr"/>
+      <c r="F4" s="0" t="inlineStr">
         <is>
           <t>468078</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>10025667</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>0.03</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>2024-01-30 15:56:21</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
+      <c r="G4" s="0" t="inlineStr">
+        <is>
+          <t>10025804</t>
+        </is>
+      </c>
+      <c r="H4" s="0" t="inlineStr">
+        <is>
+          <t>2.3</t>
+        </is>
+      </c>
+      <c r="I4" s="0" t="inlineStr">
+        <is>
+          <t>2024-05-09 15:37:30</t>
+        </is>
+      </c>
+      <c r="J4" s="0" t="inlineStr">
         <is>
           <t>第三方售卖</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="K4" s="0" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="L4" s="0" t="inlineStr">
         <is>
           <t>1999</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr"/>
-      <c r="O4" t="inlineStr">
+      <c r="M4" s="0" t="inlineStr"/>
+      <c r="O4" s="0" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>XG2024013015562113652147214</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
+      <c r="A5" s="0" t="inlineStr">
+        <is>
+          <t>XG2024050915373013652124128</t>
+        </is>
+      </c>
+      <c r="B5" s="0" t="inlineStr">
         <is>
           <t>新贵测试</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C5" s="0" t="inlineStr">
         <is>
           <t>86</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>13652147214</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr">
+      <c r="D5" s="0" t="inlineStr">
+        <is>
+          <t>13652124128</t>
+        </is>
+      </c>
+      <c r="E5" s="0" t="inlineStr"/>
+      <c r="F5" s="0" t="inlineStr">
         <is>
           <t>468078</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>10025667</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>0.03</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>2024-01-30 15:56:21</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
+      <c r="G5" s="0" t="inlineStr">
+        <is>
+          <t>10025804</t>
+        </is>
+      </c>
+      <c r="H5" s="0" t="inlineStr">
+        <is>
+          <t>2.3</t>
+        </is>
+      </c>
+      <c r="I5" s="0" t="inlineStr">
+        <is>
+          <t>2024-05-09 15:37:30</t>
+        </is>
+      </c>
+      <c r="J5" s="0" t="inlineStr">
         <is>
           <t>第三方售卖</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="K5" s="0" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="L5" s="0" t="inlineStr">
         <is>
           <t>1999</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr"/>
-      <c r="O5" t="inlineStr">
+      <c r="M5" s="0" t="inlineStr"/>
+      <c r="O5" s="0" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>XG2024013015562113652147215</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
+      <c r="A6" s="0" t="inlineStr">
+        <is>
+          <t>XG2024050915373013652124130</t>
+        </is>
+      </c>
+      <c r="B6" s="0" t="inlineStr">
         <is>
           <t>新贵测试</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C6" s="0" t="inlineStr">
         <is>
           <t>86</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>13652147215</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr">
+      <c r="D6" s="0" t="inlineStr">
+        <is>
+          <t>13652124130</t>
+        </is>
+      </c>
+      <c r="E6" s="0" t="inlineStr"/>
+      <c r="F6" s="0" t="inlineStr">
         <is>
           <t>468078</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>10025667</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>0.03</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>2024-01-30 15:56:21</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
+      <c r="G6" s="0" t="inlineStr">
+        <is>
+          <t>10025804</t>
+        </is>
+      </c>
+      <c r="H6" s="0" t="inlineStr">
+        <is>
+          <t>2.3</t>
+        </is>
+      </c>
+      <c r="I6" s="0" t="inlineStr">
+        <is>
+          <t>2024-05-09 15:37:30</t>
+        </is>
+      </c>
+      <c r="J6" s="0" t="inlineStr">
         <is>
           <t>第三方售卖</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="K6" s="0" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="L6" s="0" t="inlineStr">
         <is>
           <t>1999</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr"/>
-      <c r="O6" t="inlineStr">
+      <c r="M6" s="0" t="inlineStr"/>
+      <c r="O6" s="0" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="0" t="inlineStr">
+        <is>
+          <t>XG2024050915373013652124132</t>
+        </is>
+      </c>
+      <c r="B7" s="0" t="inlineStr">
+        <is>
+          <t>新贵测试</t>
+        </is>
+      </c>
+      <c r="C7" s="0" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="D7" s="0" t="inlineStr">
+        <is>
+          <t>13652124132</t>
+        </is>
+      </c>
+      <c r="E7" s="0" t="inlineStr"/>
+      <c r="F7" s="0" t="inlineStr">
+        <is>
+          <t>468078</t>
+        </is>
+      </c>
+      <c r="G7" s="0" t="inlineStr">
+        <is>
+          <t>10025804</t>
+        </is>
+      </c>
+      <c r="H7" s="0" t="inlineStr">
+        <is>
+          <t>2.3</t>
+        </is>
+      </c>
+      <c r="I7" s="0" t="inlineStr">
+        <is>
+          <t>2024-05-09 15:37:30</t>
+        </is>
+      </c>
+      <c r="J7" s="0" t="inlineStr">
+        <is>
+          <t>第三方售卖</t>
+        </is>
+      </c>
+      <c r="K7" s="0" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L7" s="0" t="inlineStr">
+        <is>
+          <t>1999</t>
+        </is>
+      </c>
+      <c r="M7" s="0" t="inlineStr"/>
+      <c r="O7" s="0" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="0" t="inlineStr">
+        <is>
+          <t>XG2024050915373013652124134</t>
+        </is>
+      </c>
+      <c r="B8" s="0" t="inlineStr">
+        <is>
+          <t>新贵测试</t>
+        </is>
+      </c>
+      <c r="C8" s="0" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="D8" s="0" t="inlineStr">
+        <is>
+          <t>13652124134</t>
+        </is>
+      </c>
+      <c r="E8" s="0" t="inlineStr"/>
+      <c r="F8" s="0" t="inlineStr">
+        <is>
+          <t>468078</t>
+        </is>
+      </c>
+      <c r="G8" s="0" t="inlineStr">
+        <is>
+          <t>10025804</t>
+        </is>
+      </c>
+      <c r="H8" s="0" t="inlineStr">
+        <is>
+          <t>2.3</t>
+        </is>
+      </c>
+      <c r="I8" s="0" t="inlineStr">
+        <is>
+          <t>2024-05-09 15:37:30</t>
+        </is>
+      </c>
+      <c r="J8" s="0" t="inlineStr">
+        <is>
+          <t>第三方售卖</t>
+        </is>
+      </c>
+      <c r="K8" s="0" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L8" s="0" t="inlineStr">
+        <is>
+          <t>1999</t>
+        </is>
+      </c>
+      <c r="M8" s="0" t="inlineStr"/>
+      <c r="O8" s="0" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="0" t="inlineStr">
+        <is>
+          <t>XG2024050915373013652124136</t>
+        </is>
+      </c>
+      <c r="B9" s="0" t="inlineStr">
+        <is>
+          <t>新贵测试</t>
+        </is>
+      </c>
+      <c r="C9" s="0" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="D9" s="0" t="inlineStr">
+        <is>
+          <t>13652124136</t>
+        </is>
+      </c>
+      <c r="E9" s="0" t="inlineStr"/>
+      <c r="F9" s="0" t="inlineStr">
+        <is>
+          <t>468078</t>
+        </is>
+      </c>
+      <c r="G9" s="0" t="inlineStr">
+        <is>
+          <t>10025804</t>
+        </is>
+      </c>
+      <c r="H9" s="0" t="inlineStr">
+        <is>
+          <t>2.3</t>
+        </is>
+      </c>
+      <c r="I9" s="0" t="inlineStr">
+        <is>
+          <t>2024-05-09 15:37:30</t>
+        </is>
+      </c>
+      <c r="J9" s="0" t="inlineStr">
+        <is>
+          <t>第三方售卖</t>
+        </is>
+      </c>
+      <c r="K9" s="0" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L9" s="0" t="inlineStr">
+        <is>
+          <t>1999</t>
+        </is>
+      </c>
+      <c r="M9" s="0" t="inlineStr"/>
+      <c r="O9" s="0" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="0" t="inlineStr">
+        <is>
+          <t>XG2024050915373013652124138</t>
+        </is>
+      </c>
+      <c r="B10" s="0" t="inlineStr">
+        <is>
+          <t>新贵测试</t>
+        </is>
+      </c>
+      <c r="C10" s="0" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="D10" s="0" t="inlineStr">
+        <is>
+          <t>13652124138</t>
+        </is>
+      </c>
+      <c r="E10" s="0" t="inlineStr"/>
+      <c r="F10" s="0" t="inlineStr">
+        <is>
+          <t>468078</t>
+        </is>
+      </c>
+      <c r="G10" s="0" t="inlineStr">
+        <is>
+          <t>10025804</t>
+        </is>
+      </c>
+      <c r="H10" s="0" t="inlineStr">
+        <is>
+          <t>2.3</t>
+        </is>
+      </c>
+      <c r="I10" s="0" t="inlineStr">
+        <is>
+          <t>2024-05-09 15:37:30</t>
+        </is>
+      </c>
+      <c r="J10" s="0" t="inlineStr">
+        <is>
+          <t>第三方售卖</t>
+        </is>
+      </c>
+      <c r="K10" s="0" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L10" s="0" t="inlineStr">
+        <is>
+          <t>1999</t>
+        </is>
+      </c>
+      <c r="M10" s="0" t="inlineStr"/>
+      <c r="O10" s="0" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="0" t="inlineStr">
+        <is>
+          <t>XG2024050915373013652124140</t>
+        </is>
+      </c>
+      <c r="B11" s="0" t="inlineStr">
+        <is>
+          <t>新贵测试</t>
+        </is>
+      </c>
+      <c r="C11" s="0" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="D11" s="0" t="inlineStr">
+        <is>
+          <t>13652124140</t>
+        </is>
+      </c>
+      <c r="E11" s="0" t="inlineStr"/>
+      <c r="F11" s="0" t="inlineStr">
+        <is>
+          <t>468078</t>
+        </is>
+      </c>
+      <c r="G11" s="0" t="inlineStr">
+        <is>
+          <t>10025804</t>
+        </is>
+      </c>
+      <c r="H11" s="0" t="inlineStr">
+        <is>
+          <t>2.3</t>
+        </is>
+      </c>
+      <c r="I11" s="0" t="inlineStr">
+        <is>
+          <t>2024-05-09 15:37:30</t>
+        </is>
+      </c>
+      <c r="J11" s="0" t="inlineStr">
+        <is>
+          <t>第三方售卖</t>
+        </is>
+      </c>
+      <c r="K11" s="0" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L11" s="0" t="inlineStr">
+        <is>
+          <t>1999</t>
+        </is>
+      </c>
+      <c r="M11" s="0" t="inlineStr"/>
+      <c r="O11" s="0" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="0" t="inlineStr">
+        <is>
+          <t>XG2024050915373013652124142</t>
+        </is>
+      </c>
+      <c r="B12" s="0" t="inlineStr">
+        <is>
+          <t>新贵测试</t>
+        </is>
+      </c>
+      <c r="C12" s="0" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="D12" s="0" t="inlineStr">
+        <is>
+          <t>13652124142</t>
+        </is>
+      </c>
+      <c r="E12" s="0" t="inlineStr"/>
+      <c r="F12" s="0" t="inlineStr">
+        <is>
+          <t>468078</t>
+        </is>
+      </c>
+      <c r="G12" s="0" t="inlineStr">
+        <is>
+          <t>10025804</t>
+        </is>
+      </c>
+      <c r="H12" s="0" t="inlineStr">
+        <is>
+          <t>2.3</t>
+        </is>
+      </c>
+      <c r="I12" s="0" t="inlineStr">
+        <is>
+          <t>2024-05-09 15:37:30</t>
+        </is>
+      </c>
+      <c r="J12" s="0" t="inlineStr">
+        <is>
+          <t>第三方售卖</t>
+        </is>
+      </c>
+      <c r="K12" s="0" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L12" s="0" t="inlineStr">
+        <is>
+          <t>1999</t>
+        </is>
+      </c>
+      <c r="M12" s="0" t="inlineStr"/>
+      <c r="O12" s="0" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="0" t="inlineStr">
+        <is>
+          <t>XG2024050915373013652124144</t>
+        </is>
+      </c>
+      <c r="B13" s="0" t="inlineStr">
+        <is>
+          <t>新贵测试</t>
+        </is>
+      </c>
+      <c r="C13" s="0" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="D13" s="0" t="inlineStr">
+        <is>
+          <t>13652124144</t>
+        </is>
+      </c>
+      <c r="E13" s="0" t="inlineStr"/>
+      <c r="F13" s="0" t="inlineStr">
+        <is>
+          <t>468078</t>
+        </is>
+      </c>
+      <c r="G13" s="0" t="inlineStr">
+        <is>
+          <t>10025804</t>
+        </is>
+      </c>
+      <c r="H13" s="0" t="inlineStr">
+        <is>
+          <t>2.3</t>
+        </is>
+      </c>
+      <c r="I13" s="0" t="inlineStr">
+        <is>
+          <t>2024-05-09 15:37:30</t>
+        </is>
+      </c>
+      <c r="J13" s="0" t="inlineStr">
+        <is>
+          <t>第三方售卖</t>
+        </is>
+      </c>
+      <c r="K13" s="0" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L13" s="0" t="inlineStr">
+        <is>
+          <t>1999</t>
+        </is>
+      </c>
+      <c r="M13" s="0" t="inlineStr"/>
+      <c r="O13" s="0" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="0" t="inlineStr">
+        <is>
+          <t>XG2024050915373013652124146</t>
+        </is>
+      </c>
+      <c r="B14" s="0" t="inlineStr">
+        <is>
+          <t>新贵测试</t>
+        </is>
+      </c>
+      <c r="C14" s="0" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="D14" s="0" t="inlineStr">
+        <is>
+          <t>13652124146</t>
+        </is>
+      </c>
+      <c r="E14" s="0" t="inlineStr"/>
+      <c r="F14" s="0" t="inlineStr">
+        <is>
+          <t>468078</t>
+        </is>
+      </c>
+      <c r="G14" s="0" t="inlineStr">
+        <is>
+          <t>10025804</t>
+        </is>
+      </c>
+      <c r="H14" s="0" t="inlineStr">
+        <is>
+          <t>2.3</t>
+        </is>
+      </c>
+      <c r="I14" s="0" t="inlineStr">
+        <is>
+          <t>2024-05-09 15:37:30</t>
+        </is>
+      </c>
+      <c r="J14" s="0" t="inlineStr">
+        <is>
+          <t>第三方售卖</t>
+        </is>
+      </c>
+      <c r="K14" s="0" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L14" s="0" t="inlineStr">
+        <is>
+          <t>1999</t>
+        </is>
+      </c>
+      <c r="M14" s="0" t="inlineStr"/>
+      <c r="O14" s="0" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="0" t="inlineStr">
+        <is>
+          <t>XG2024050915373014466227693</t>
+        </is>
+      </c>
+      <c r="B15" s="0" t="inlineStr">
+        <is>
+          <t>新贵测试</t>
+        </is>
+      </c>
+      <c r="C15" s="0" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="D15" s="0" t="inlineStr">
+        <is>
+          <t>14466227693</t>
+        </is>
+      </c>
+      <c r="E15" s="0" t="inlineStr"/>
+      <c r="F15" s="0" t="inlineStr">
+        <is>
+          <t>468078</t>
+        </is>
+      </c>
+      <c r="G15" s="0" t="inlineStr">
+        <is>
+          <t>10025804</t>
+        </is>
+      </c>
+      <c r="H15" s="0" t="inlineStr">
+        <is>
+          <t>2.3</t>
+        </is>
+      </c>
+      <c r="I15" s="0" t="inlineStr">
+        <is>
+          <t>2024-05-09 15:37:30</t>
+        </is>
+      </c>
+      <c r="J15" s="0" t="inlineStr">
+        <is>
+          <t>第三方售卖</t>
+        </is>
+      </c>
+      <c r="K15" s="0" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L15" s="0" t="inlineStr">
+        <is>
+          <t>1999</t>
+        </is>
+      </c>
+      <c r="M15" s="0" t="inlineStr"/>
+      <c r="O15" s="0" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="0" t="inlineStr">
+        <is>
+          <t>XG2024050915373014055501045</t>
+        </is>
+      </c>
+      <c r="B16" s="0" t="inlineStr">
+        <is>
+          <t>新贵测试</t>
+        </is>
+      </c>
+      <c r="C16" s="0" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="D16" s="0" t="inlineStr">
+        <is>
+          <t>14055501045</t>
+        </is>
+      </c>
+      <c r="E16" s="0" t="inlineStr"/>
+      <c r="F16" s="0" t="inlineStr">
+        <is>
+          <t>468078</t>
+        </is>
+      </c>
+      <c r="G16" s="0" t="inlineStr">
+        <is>
+          <t>10025804</t>
+        </is>
+      </c>
+      <c r="H16" s="0" t="inlineStr">
+        <is>
+          <t>2.3</t>
+        </is>
+      </c>
+      <c r="I16" s="0" t="inlineStr">
+        <is>
+          <t>2024-05-09 15:37:30</t>
+        </is>
+      </c>
+      <c r="J16" s="0" t="inlineStr">
+        <is>
+          <t>第三方售卖</t>
+        </is>
+      </c>
+      <c r="K16" s="0" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L16" s="0" t="inlineStr">
+        <is>
+          <t>1999</t>
+        </is>
+      </c>
+      <c r="M16" s="0" t="inlineStr"/>
+      <c r="O16" s="0" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="0" t="inlineStr">
+        <is>
+          <t>XG2024050915373018818810933</t>
+        </is>
+      </c>
+      <c r="B17" s="0" t="inlineStr">
+        <is>
+          <t>新贵测试</t>
+        </is>
+      </c>
+      <c r="C17" s="0" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="D17" s="0" t="inlineStr">
+        <is>
+          <t>18818810933</t>
+        </is>
+      </c>
+      <c r="E17" s="0" t="inlineStr"/>
+      <c r="F17" s="0" t="inlineStr">
+        <is>
+          <t>468078</t>
+        </is>
+      </c>
+      <c r="G17" s="0" t="inlineStr">
+        <is>
+          <t>10025804</t>
+        </is>
+      </c>
+      <c r="H17" s="0" t="inlineStr">
+        <is>
+          <t>2.3</t>
+        </is>
+      </c>
+      <c r="I17" s="0" t="inlineStr">
+        <is>
+          <t>2024-05-09 15:37:30</t>
+        </is>
+      </c>
+      <c r="J17" s="0" t="inlineStr">
+        <is>
+          <t>第三方售卖</t>
+        </is>
+      </c>
+      <c r="K17" s="0" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L17" s="0" t="inlineStr">
+        <is>
+          <t>1999</t>
+        </is>
+      </c>
+      <c r="M17" s="0" t="inlineStr"/>
+      <c r="O17" s="0" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="0" t="inlineStr">
+        <is>
+          <t>XG2024050915373014423960806</t>
+        </is>
+      </c>
+      <c r="B18" s="0" t="inlineStr">
+        <is>
+          <t>新贵测试</t>
+        </is>
+      </c>
+      <c r="C18" s="0" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="D18" s="0" t="inlineStr">
+        <is>
+          <t>14423960806</t>
+        </is>
+      </c>
+      <c r="E18" s="0" t="inlineStr"/>
+      <c r="F18" s="0" t="inlineStr">
+        <is>
+          <t>468078</t>
+        </is>
+      </c>
+      <c r="G18" s="0" t="inlineStr">
+        <is>
+          <t>10025804</t>
+        </is>
+      </c>
+      <c r="H18" s="0" t="inlineStr">
+        <is>
+          <t>2.3</t>
+        </is>
+      </c>
+      <c r="I18" s="0" t="inlineStr">
+        <is>
+          <t>2024-05-09 15:37:30</t>
+        </is>
+      </c>
+      <c r="J18" s="0" t="inlineStr">
+        <is>
+          <t>第三方售卖</t>
+        </is>
+      </c>
+      <c r="K18" s="0" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L18" s="0" t="inlineStr">
+        <is>
+          <t>1999</t>
+        </is>
+      </c>
+      <c r="M18" s="0" t="inlineStr"/>
+      <c r="O18" s="0" t="inlineStr">
         <is>
           <t>0</t>
         </is>

--- a/API/CreateData/yizhi.xlsx
+++ b/API/CreateData/yizhi.xlsx
@@ -1342,7 +1342,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W18"/>
+  <dimension ref="A1:W3"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="15" outlineLevelRow="1"/>
   <cols>
     <col width="35.9166666666667" customWidth="1" style="1" min="1" max="1"/>
@@ -1488,7 +1488,7 @@
     <row r="3">
       <c r="A3" s="0" t="inlineStr">
         <is>
-          <t>XG2024051416323915594083772</t>
+          <t>XG2024111814005215204025100</t>
         </is>
       </c>
       <c r="B3" s="0" t="inlineStr">
@@ -1503,7 +1503,7 @@
       </c>
       <c r="D3" s="0" t="inlineStr">
         <is>
-          <t>15594083772</t>
+          <t>15204025100</t>
         </is>
       </c>
       <c r="E3" s="0" t="inlineStr"/>
@@ -1514,17 +1514,17 @@
       </c>
       <c r="G3" s="0" t="inlineStr">
         <is>
-          <t>10025804</t>
+          <t>10016745</t>
         </is>
       </c>
       <c r="H3" s="0" t="inlineStr">
         <is>
-          <t>2.3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I3" s="0" t="inlineStr">
         <is>
-          <t>2024-05-14 16:32:39</t>
+          <t>2024-11-18 14:00:52</t>
         </is>
       </c>
       <c r="J3" s="0" t="inlineStr">
@@ -1544,966 +1544,6 @@
       </c>
       <c r="M3" s="0" t="inlineStr"/>
       <c r="O3" s="0" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="0" t="inlineStr">
-        <is>
-          <t>XG2024050915373013652124126</t>
-        </is>
-      </c>
-      <c r="B4" s="0" t="inlineStr">
-        <is>
-          <t>新贵测试</t>
-        </is>
-      </c>
-      <c r="C4" s="0" t="inlineStr">
-        <is>
-          <t>86</t>
-        </is>
-      </c>
-      <c r="D4" s="0" t="inlineStr">
-        <is>
-          <t>13652124126</t>
-        </is>
-      </c>
-      <c r="E4" s="0" t="inlineStr"/>
-      <c r="F4" s="0" t="inlineStr">
-        <is>
-          <t>468078</t>
-        </is>
-      </c>
-      <c r="G4" s="0" t="inlineStr">
-        <is>
-          <t>10025804</t>
-        </is>
-      </c>
-      <c r="H4" s="0" t="inlineStr">
-        <is>
-          <t>2.3</t>
-        </is>
-      </c>
-      <c r="I4" s="0" t="inlineStr">
-        <is>
-          <t>2024-05-09 15:37:30</t>
-        </is>
-      </c>
-      <c r="J4" s="0" t="inlineStr">
-        <is>
-          <t>第三方售卖</t>
-        </is>
-      </c>
-      <c r="K4" s="0" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L4" s="0" t="inlineStr">
-        <is>
-          <t>1999</t>
-        </is>
-      </c>
-      <c r="M4" s="0" t="inlineStr"/>
-      <c r="O4" s="0" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="0" t="inlineStr">
-        <is>
-          <t>XG2024050915373013652124128</t>
-        </is>
-      </c>
-      <c r="B5" s="0" t="inlineStr">
-        <is>
-          <t>新贵测试</t>
-        </is>
-      </c>
-      <c r="C5" s="0" t="inlineStr">
-        <is>
-          <t>86</t>
-        </is>
-      </c>
-      <c r="D5" s="0" t="inlineStr">
-        <is>
-          <t>13652124128</t>
-        </is>
-      </c>
-      <c r="E5" s="0" t="inlineStr"/>
-      <c r="F5" s="0" t="inlineStr">
-        <is>
-          <t>468078</t>
-        </is>
-      </c>
-      <c r="G5" s="0" t="inlineStr">
-        <is>
-          <t>10025804</t>
-        </is>
-      </c>
-      <c r="H5" s="0" t="inlineStr">
-        <is>
-          <t>2.3</t>
-        </is>
-      </c>
-      <c r="I5" s="0" t="inlineStr">
-        <is>
-          <t>2024-05-09 15:37:30</t>
-        </is>
-      </c>
-      <c r="J5" s="0" t="inlineStr">
-        <is>
-          <t>第三方售卖</t>
-        </is>
-      </c>
-      <c r="K5" s="0" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L5" s="0" t="inlineStr">
-        <is>
-          <t>1999</t>
-        </is>
-      </c>
-      <c r="M5" s="0" t="inlineStr"/>
-      <c r="O5" s="0" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="0" t="inlineStr">
-        <is>
-          <t>XG2024050915373013652124130</t>
-        </is>
-      </c>
-      <c r="B6" s="0" t="inlineStr">
-        <is>
-          <t>新贵测试</t>
-        </is>
-      </c>
-      <c r="C6" s="0" t="inlineStr">
-        <is>
-          <t>86</t>
-        </is>
-      </c>
-      <c r="D6" s="0" t="inlineStr">
-        <is>
-          <t>13652124130</t>
-        </is>
-      </c>
-      <c r="E6" s="0" t="inlineStr"/>
-      <c r="F6" s="0" t="inlineStr">
-        <is>
-          <t>468078</t>
-        </is>
-      </c>
-      <c r="G6" s="0" t="inlineStr">
-        <is>
-          <t>10025804</t>
-        </is>
-      </c>
-      <c r="H6" s="0" t="inlineStr">
-        <is>
-          <t>2.3</t>
-        </is>
-      </c>
-      <c r="I6" s="0" t="inlineStr">
-        <is>
-          <t>2024-05-09 15:37:30</t>
-        </is>
-      </c>
-      <c r="J6" s="0" t="inlineStr">
-        <is>
-          <t>第三方售卖</t>
-        </is>
-      </c>
-      <c r="K6" s="0" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L6" s="0" t="inlineStr">
-        <is>
-          <t>1999</t>
-        </is>
-      </c>
-      <c r="M6" s="0" t="inlineStr"/>
-      <c r="O6" s="0" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="0" t="inlineStr">
-        <is>
-          <t>XG2024050915373013652124132</t>
-        </is>
-      </c>
-      <c r="B7" s="0" t="inlineStr">
-        <is>
-          <t>新贵测试</t>
-        </is>
-      </c>
-      <c r="C7" s="0" t="inlineStr">
-        <is>
-          <t>86</t>
-        </is>
-      </c>
-      <c r="D7" s="0" t="inlineStr">
-        <is>
-          <t>13652124132</t>
-        </is>
-      </c>
-      <c r="E7" s="0" t="inlineStr"/>
-      <c r="F7" s="0" t="inlineStr">
-        <is>
-          <t>468078</t>
-        </is>
-      </c>
-      <c r="G7" s="0" t="inlineStr">
-        <is>
-          <t>10025804</t>
-        </is>
-      </c>
-      <c r="H7" s="0" t="inlineStr">
-        <is>
-          <t>2.3</t>
-        </is>
-      </c>
-      <c r="I7" s="0" t="inlineStr">
-        <is>
-          <t>2024-05-09 15:37:30</t>
-        </is>
-      </c>
-      <c r="J7" s="0" t="inlineStr">
-        <is>
-          <t>第三方售卖</t>
-        </is>
-      </c>
-      <c r="K7" s="0" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L7" s="0" t="inlineStr">
-        <is>
-          <t>1999</t>
-        </is>
-      </c>
-      <c r="M7" s="0" t="inlineStr"/>
-      <c r="O7" s="0" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="0" t="inlineStr">
-        <is>
-          <t>XG2024050915373013652124134</t>
-        </is>
-      </c>
-      <c r="B8" s="0" t="inlineStr">
-        <is>
-          <t>新贵测试</t>
-        </is>
-      </c>
-      <c r="C8" s="0" t="inlineStr">
-        <is>
-          <t>86</t>
-        </is>
-      </c>
-      <c r="D8" s="0" t="inlineStr">
-        <is>
-          <t>13652124134</t>
-        </is>
-      </c>
-      <c r="E8" s="0" t="inlineStr"/>
-      <c r="F8" s="0" t="inlineStr">
-        <is>
-          <t>468078</t>
-        </is>
-      </c>
-      <c r="G8" s="0" t="inlineStr">
-        <is>
-          <t>10025804</t>
-        </is>
-      </c>
-      <c r="H8" s="0" t="inlineStr">
-        <is>
-          <t>2.3</t>
-        </is>
-      </c>
-      <c r="I8" s="0" t="inlineStr">
-        <is>
-          <t>2024-05-09 15:37:30</t>
-        </is>
-      </c>
-      <c r="J8" s="0" t="inlineStr">
-        <is>
-          <t>第三方售卖</t>
-        </is>
-      </c>
-      <c r="K8" s="0" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L8" s="0" t="inlineStr">
-        <is>
-          <t>1999</t>
-        </is>
-      </c>
-      <c r="M8" s="0" t="inlineStr"/>
-      <c r="O8" s="0" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="0" t="inlineStr">
-        <is>
-          <t>XG2024050915373013652124136</t>
-        </is>
-      </c>
-      <c r="B9" s="0" t="inlineStr">
-        <is>
-          <t>新贵测试</t>
-        </is>
-      </c>
-      <c r="C9" s="0" t="inlineStr">
-        <is>
-          <t>86</t>
-        </is>
-      </c>
-      <c r="D9" s="0" t="inlineStr">
-        <is>
-          <t>13652124136</t>
-        </is>
-      </c>
-      <c r="E9" s="0" t="inlineStr"/>
-      <c r="F9" s="0" t="inlineStr">
-        <is>
-          <t>468078</t>
-        </is>
-      </c>
-      <c r="G9" s="0" t="inlineStr">
-        <is>
-          <t>10025804</t>
-        </is>
-      </c>
-      <c r="H9" s="0" t="inlineStr">
-        <is>
-          <t>2.3</t>
-        </is>
-      </c>
-      <c r="I9" s="0" t="inlineStr">
-        <is>
-          <t>2024-05-09 15:37:30</t>
-        </is>
-      </c>
-      <c r="J9" s="0" t="inlineStr">
-        <is>
-          <t>第三方售卖</t>
-        </is>
-      </c>
-      <c r="K9" s="0" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L9" s="0" t="inlineStr">
-        <is>
-          <t>1999</t>
-        </is>
-      </c>
-      <c r="M9" s="0" t="inlineStr"/>
-      <c r="O9" s="0" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="0" t="inlineStr">
-        <is>
-          <t>XG2024050915373013652124138</t>
-        </is>
-      </c>
-      <c r="B10" s="0" t="inlineStr">
-        <is>
-          <t>新贵测试</t>
-        </is>
-      </c>
-      <c r="C10" s="0" t="inlineStr">
-        <is>
-          <t>86</t>
-        </is>
-      </c>
-      <c r="D10" s="0" t="inlineStr">
-        <is>
-          <t>13652124138</t>
-        </is>
-      </c>
-      <c r="E10" s="0" t="inlineStr"/>
-      <c r="F10" s="0" t="inlineStr">
-        <is>
-          <t>468078</t>
-        </is>
-      </c>
-      <c r="G10" s="0" t="inlineStr">
-        <is>
-          <t>10025804</t>
-        </is>
-      </c>
-      <c r="H10" s="0" t="inlineStr">
-        <is>
-          <t>2.3</t>
-        </is>
-      </c>
-      <c r="I10" s="0" t="inlineStr">
-        <is>
-          <t>2024-05-09 15:37:30</t>
-        </is>
-      </c>
-      <c r="J10" s="0" t="inlineStr">
-        <is>
-          <t>第三方售卖</t>
-        </is>
-      </c>
-      <c r="K10" s="0" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L10" s="0" t="inlineStr">
-        <is>
-          <t>1999</t>
-        </is>
-      </c>
-      <c r="M10" s="0" t="inlineStr"/>
-      <c r="O10" s="0" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="0" t="inlineStr">
-        <is>
-          <t>XG2024050915373013652124140</t>
-        </is>
-      </c>
-      <c r="B11" s="0" t="inlineStr">
-        <is>
-          <t>新贵测试</t>
-        </is>
-      </c>
-      <c r="C11" s="0" t="inlineStr">
-        <is>
-          <t>86</t>
-        </is>
-      </c>
-      <c r="D11" s="0" t="inlineStr">
-        <is>
-          <t>13652124140</t>
-        </is>
-      </c>
-      <c r="E11" s="0" t="inlineStr"/>
-      <c r="F11" s="0" t="inlineStr">
-        <is>
-          <t>468078</t>
-        </is>
-      </c>
-      <c r="G11" s="0" t="inlineStr">
-        <is>
-          <t>10025804</t>
-        </is>
-      </c>
-      <c r="H11" s="0" t="inlineStr">
-        <is>
-          <t>2.3</t>
-        </is>
-      </c>
-      <c r="I11" s="0" t="inlineStr">
-        <is>
-          <t>2024-05-09 15:37:30</t>
-        </is>
-      </c>
-      <c r="J11" s="0" t="inlineStr">
-        <is>
-          <t>第三方售卖</t>
-        </is>
-      </c>
-      <c r="K11" s="0" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L11" s="0" t="inlineStr">
-        <is>
-          <t>1999</t>
-        </is>
-      </c>
-      <c r="M11" s="0" t="inlineStr"/>
-      <c r="O11" s="0" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="0" t="inlineStr">
-        <is>
-          <t>XG2024050915373013652124142</t>
-        </is>
-      </c>
-      <c r="B12" s="0" t="inlineStr">
-        <is>
-          <t>新贵测试</t>
-        </is>
-      </c>
-      <c r="C12" s="0" t="inlineStr">
-        <is>
-          <t>86</t>
-        </is>
-      </c>
-      <c r="D12" s="0" t="inlineStr">
-        <is>
-          <t>13652124142</t>
-        </is>
-      </c>
-      <c r="E12" s="0" t="inlineStr"/>
-      <c r="F12" s="0" t="inlineStr">
-        <is>
-          <t>468078</t>
-        </is>
-      </c>
-      <c r="G12" s="0" t="inlineStr">
-        <is>
-          <t>10025804</t>
-        </is>
-      </c>
-      <c r="H12" s="0" t="inlineStr">
-        <is>
-          <t>2.3</t>
-        </is>
-      </c>
-      <c r="I12" s="0" t="inlineStr">
-        <is>
-          <t>2024-05-09 15:37:30</t>
-        </is>
-      </c>
-      <c r="J12" s="0" t="inlineStr">
-        <is>
-          <t>第三方售卖</t>
-        </is>
-      </c>
-      <c r="K12" s="0" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L12" s="0" t="inlineStr">
-        <is>
-          <t>1999</t>
-        </is>
-      </c>
-      <c r="M12" s="0" t="inlineStr"/>
-      <c r="O12" s="0" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="0" t="inlineStr">
-        <is>
-          <t>XG2024050915373013652124144</t>
-        </is>
-      </c>
-      <c r="B13" s="0" t="inlineStr">
-        <is>
-          <t>新贵测试</t>
-        </is>
-      </c>
-      <c r="C13" s="0" t="inlineStr">
-        <is>
-          <t>86</t>
-        </is>
-      </c>
-      <c r="D13" s="0" t="inlineStr">
-        <is>
-          <t>13652124144</t>
-        </is>
-      </c>
-      <c r="E13" s="0" t="inlineStr"/>
-      <c r="F13" s="0" t="inlineStr">
-        <is>
-          <t>468078</t>
-        </is>
-      </c>
-      <c r="G13" s="0" t="inlineStr">
-        <is>
-          <t>10025804</t>
-        </is>
-      </c>
-      <c r="H13" s="0" t="inlineStr">
-        <is>
-          <t>2.3</t>
-        </is>
-      </c>
-      <c r="I13" s="0" t="inlineStr">
-        <is>
-          <t>2024-05-09 15:37:30</t>
-        </is>
-      </c>
-      <c r="J13" s="0" t="inlineStr">
-        <is>
-          <t>第三方售卖</t>
-        </is>
-      </c>
-      <c r="K13" s="0" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L13" s="0" t="inlineStr">
-        <is>
-          <t>1999</t>
-        </is>
-      </c>
-      <c r="M13" s="0" t="inlineStr"/>
-      <c r="O13" s="0" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="0" t="inlineStr">
-        <is>
-          <t>XG2024050915373013652124146</t>
-        </is>
-      </c>
-      <c r="B14" s="0" t="inlineStr">
-        <is>
-          <t>新贵测试</t>
-        </is>
-      </c>
-      <c r="C14" s="0" t="inlineStr">
-        <is>
-          <t>86</t>
-        </is>
-      </c>
-      <c r="D14" s="0" t="inlineStr">
-        <is>
-          <t>13652124146</t>
-        </is>
-      </c>
-      <c r="E14" s="0" t="inlineStr"/>
-      <c r="F14" s="0" t="inlineStr">
-        <is>
-          <t>468078</t>
-        </is>
-      </c>
-      <c r="G14" s="0" t="inlineStr">
-        <is>
-          <t>10025804</t>
-        </is>
-      </c>
-      <c r="H14" s="0" t="inlineStr">
-        <is>
-          <t>2.3</t>
-        </is>
-      </c>
-      <c r="I14" s="0" t="inlineStr">
-        <is>
-          <t>2024-05-09 15:37:30</t>
-        </is>
-      </c>
-      <c r="J14" s="0" t="inlineStr">
-        <is>
-          <t>第三方售卖</t>
-        </is>
-      </c>
-      <c r="K14" s="0" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L14" s="0" t="inlineStr">
-        <is>
-          <t>1999</t>
-        </is>
-      </c>
-      <c r="M14" s="0" t="inlineStr"/>
-      <c r="O14" s="0" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="0" t="inlineStr">
-        <is>
-          <t>XG2024050915373014466227693</t>
-        </is>
-      </c>
-      <c r="B15" s="0" t="inlineStr">
-        <is>
-          <t>新贵测试</t>
-        </is>
-      </c>
-      <c r="C15" s="0" t="inlineStr">
-        <is>
-          <t>86</t>
-        </is>
-      </c>
-      <c r="D15" s="0" t="inlineStr">
-        <is>
-          <t>14466227693</t>
-        </is>
-      </c>
-      <c r="E15" s="0" t="inlineStr"/>
-      <c r="F15" s="0" t="inlineStr">
-        <is>
-          <t>468078</t>
-        </is>
-      </c>
-      <c r="G15" s="0" t="inlineStr">
-        <is>
-          <t>10025804</t>
-        </is>
-      </c>
-      <c r="H15" s="0" t="inlineStr">
-        <is>
-          <t>2.3</t>
-        </is>
-      </c>
-      <c r="I15" s="0" t="inlineStr">
-        <is>
-          <t>2024-05-09 15:37:30</t>
-        </is>
-      </c>
-      <c r="J15" s="0" t="inlineStr">
-        <is>
-          <t>第三方售卖</t>
-        </is>
-      </c>
-      <c r="K15" s="0" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L15" s="0" t="inlineStr">
-        <is>
-          <t>1999</t>
-        </is>
-      </c>
-      <c r="M15" s="0" t="inlineStr"/>
-      <c r="O15" s="0" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="0" t="inlineStr">
-        <is>
-          <t>XG2024050915373014055501045</t>
-        </is>
-      </c>
-      <c r="B16" s="0" t="inlineStr">
-        <is>
-          <t>新贵测试</t>
-        </is>
-      </c>
-      <c r="C16" s="0" t="inlineStr">
-        <is>
-          <t>86</t>
-        </is>
-      </c>
-      <c r="D16" s="0" t="inlineStr">
-        <is>
-          <t>14055501045</t>
-        </is>
-      </c>
-      <c r="E16" s="0" t="inlineStr"/>
-      <c r="F16" s="0" t="inlineStr">
-        <is>
-          <t>468078</t>
-        </is>
-      </c>
-      <c r="G16" s="0" t="inlineStr">
-        <is>
-          <t>10025804</t>
-        </is>
-      </c>
-      <c r="H16" s="0" t="inlineStr">
-        <is>
-          <t>2.3</t>
-        </is>
-      </c>
-      <c r="I16" s="0" t="inlineStr">
-        <is>
-          <t>2024-05-09 15:37:30</t>
-        </is>
-      </c>
-      <c r="J16" s="0" t="inlineStr">
-        <is>
-          <t>第三方售卖</t>
-        </is>
-      </c>
-      <c r="K16" s="0" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L16" s="0" t="inlineStr">
-        <is>
-          <t>1999</t>
-        </is>
-      </c>
-      <c r="M16" s="0" t="inlineStr"/>
-      <c r="O16" s="0" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="0" t="inlineStr">
-        <is>
-          <t>XG2024050915373018818810933</t>
-        </is>
-      </c>
-      <c r="B17" s="0" t="inlineStr">
-        <is>
-          <t>新贵测试</t>
-        </is>
-      </c>
-      <c r="C17" s="0" t="inlineStr">
-        <is>
-          <t>86</t>
-        </is>
-      </c>
-      <c r="D17" s="0" t="inlineStr">
-        <is>
-          <t>18818810933</t>
-        </is>
-      </c>
-      <c r="E17" s="0" t="inlineStr"/>
-      <c r="F17" s="0" t="inlineStr">
-        <is>
-          <t>468078</t>
-        </is>
-      </c>
-      <c r="G17" s="0" t="inlineStr">
-        <is>
-          <t>10025804</t>
-        </is>
-      </c>
-      <c r="H17" s="0" t="inlineStr">
-        <is>
-          <t>2.3</t>
-        </is>
-      </c>
-      <c r="I17" s="0" t="inlineStr">
-        <is>
-          <t>2024-05-09 15:37:30</t>
-        </is>
-      </c>
-      <c r="J17" s="0" t="inlineStr">
-        <is>
-          <t>第三方售卖</t>
-        </is>
-      </c>
-      <c r="K17" s="0" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L17" s="0" t="inlineStr">
-        <is>
-          <t>1999</t>
-        </is>
-      </c>
-      <c r="M17" s="0" t="inlineStr"/>
-      <c r="O17" s="0" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="0" t="inlineStr">
-        <is>
-          <t>XG2024050915373014423960806</t>
-        </is>
-      </c>
-      <c r="B18" s="0" t="inlineStr">
-        <is>
-          <t>新贵测试</t>
-        </is>
-      </c>
-      <c r="C18" s="0" t="inlineStr">
-        <is>
-          <t>86</t>
-        </is>
-      </c>
-      <c r="D18" s="0" t="inlineStr">
-        <is>
-          <t>14423960806</t>
-        </is>
-      </c>
-      <c r="E18" s="0" t="inlineStr"/>
-      <c r="F18" s="0" t="inlineStr">
-        <is>
-          <t>468078</t>
-        </is>
-      </c>
-      <c r="G18" s="0" t="inlineStr">
-        <is>
-          <t>10025804</t>
-        </is>
-      </c>
-      <c r="H18" s="0" t="inlineStr">
-        <is>
-          <t>2.3</t>
-        </is>
-      </c>
-      <c r="I18" s="0" t="inlineStr">
-        <is>
-          <t>2024-05-09 15:37:30</t>
-        </is>
-      </c>
-      <c r="J18" s="0" t="inlineStr">
-        <is>
-          <t>第三方售卖</t>
-        </is>
-      </c>
-      <c r="K18" s="0" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L18" s="0" t="inlineStr">
-        <is>
-          <t>1999</t>
-        </is>
-      </c>
-      <c r="M18" s="0" t="inlineStr"/>
-      <c r="O18" s="0" t="inlineStr">
         <is>
           <t>0</t>
         </is>

--- a/API/CreateData/yizhi.xlsx
+++ b/API/CreateData/yizhi.xlsx
@@ -1488,7 +1488,7 @@
     <row r="3">
       <c r="A3" s="0" t="inlineStr">
         <is>
-          <t>XG2024111814005215204025100</t>
+          <t>XG2024112618241017198966518</t>
         </is>
       </c>
       <c r="B3" s="0" t="inlineStr">
@@ -1503,7 +1503,7 @@
       </c>
       <c r="D3" s="0" t="inlineStr">
         <is>
-          <t>15204025100</t>
+          <t>17198966518</t>
         </is>
       </c>
       <c r="E3" s="0" t="inlineStr"/>
@@ -1514,17 +1514,17 @@
       </c>
       <c r="G3" s="0" t="inlineStr">
         <is>
-          <t>10016745</t>
+          <t>10025804</t>
         </is>
       </c>
       <c r="H3" s="0" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2.3</t>
         </is>
       </c>
       <c r="I3" s="0" t="inlineStr">
         <is>
-          <t>2024-11-18 14:00:52</t>
+          <t>2024-11-26 18:24:10</t>
         </is>
       </c>
       <c r="J3" s="0" t="inlineStr">

--- a/API/CreateData/yizhi.xlsx
+++ b/API/CreateData/yizhi.xlsx
@@ -1488,7 +1488,7 @@
     <row r="3">
       <c r="A3" s="0" t="inlineStr">
         <is>
-          <t>XG2024112618241017198966518</t>
+          <t>XG2024120617302417423915421</t>
         </is>
       </c>
       <c r="B3" s="0" t="inlineStr">
@@ -1503,7 +1503,7 @@
       </c>
       <c r="D3" s="0" t="inlineStr">
         <is>
-          <t>17198966518</t>
+          <t>17423915421</t>
         </is>
       </c>
       <c r="E3" s="0" t="inlineStr"/>
@@ -1524,7 +1524,7 @@
       </c>
       <c r="I3" s="0" t="inlineStr">
         <is>
-          <t>2024-11-26 18:24:10</t>
+          <t>2024-12-06 17:30:24</t>
         </is>
       </c>
       <c r="J3" s="0" t="inlineStr">

--- a/API/CreateData/yizhi.xlsx
+++ b/API/CreateData/yizhi.xlsx
@@ -1488,7 +1488,7 @@
     <row r="3">
       <c r="A3" s="0" t="inlineStr">
         <is>
-          <t>XG2024120617302417423915421</t>
+          <t>XG2024121616283717170864332</t>
         </is>
       </c>
       <c r="B3" s="0" t="inlineStr">
@@ -1503,7 +1503,7 @@
       </c>
       <c r="D3" s="0" t="inlineStr">
         <is>
-          <t>17423915421</t>
+          <t>17170864332</t>
         </is>
       </c>
       <c r="E3" s="0" t="inlineStr"/>
@@ -1524,7 +1524,7 @@
       </c>
       <c r="I3" s="0" t="inlineStr">
         <is>
-          <t>2024-12-06 17:30:24</t>
+          <t>2024-12-16 16:28:37</t>
         </is>
       </c>
       <c r="J3" s="0" t="inlineStr">

--- a/API/CreateData/yizhi.xlsx
+++ b/API/CreateData/yizhi.xlsx
@@ -1488,7 +1488,7 @@
     <row r="3">
       <c r="A3" s="0" t="inlineStr">
         <is>
-          <t>XG2024121616283717170864332</t>
+          <t>XG2024121810255218707699952</t>
         </is>
       </c>
       <c r="B3" s="0" t="inlineStr">
@@ -1503,7 +1503,7 @@
       </c>
       <c r="D3" s="0" t="inlineStr">
         <is>
-          <t>17170864332</t>
+          <t>18707699952</t>
         </is>
       </c>
       <c r="E3" s="0" t="inlineStr"/>
@@ -1524,7 +1524,7 @@
       </c>
       <c r="I3" s="0" t="inlineStr">
         <is>
-          <t>2024-12-16 16:28:37</t>
+          <t>2024-12-18 10:25:52</t>
         </is>
       </c>
       <c r="J3" s="0" t="inlineStr">

--- a/API/CreateData/yizhi.xlsx
+++ b/API/CreateData/yizhi.xlsx
@@ -1488,7 +1488,7 @@
     <row r="3">
       <c r="A3" s="0" t="inlineStr">
         <is>
-          <t>XG2024121810255218707699952</t>
+          <t>XG2024121820521616336721691</t>
         </is>
       </c>
       <c r="B3" s="0" t="inlineStr">
@@ -1503,7 +1503,7 @@
       </c>
       <c r="D3" s="0" t="inlineStr">
         <is>
-          <t>18707699952</t>
+          <t>16336721691</t>
         </is>
       </c>
       <c r="E3" s="0" t="inlineStr"/>
@@ -1524,7 +1524,7 @@
       </c>
       <c r="I3" s="0" t="inlineStr">
         <is>
-          <t>2024-12-18 10:25:52</t>
+          <t>2024-12-18 20:52:16</t>
         </is>
       </c>
       <c r="J3" s="0" t="inlineStr">

--- a/API/CreateData/yizhi.xlsx
+++ b/API/CreateData/yizhi.xlsx
@@ -1488,7 +1488,7 @@
     <row r="3">
       <c r="A3" s="0" t="inlineStr">
         <is>
-          <t>XG2024121820521616336721691</t>
+          <t>XG2024122616082814660206373</t>
         </is>
       </c>
       <c r="B3" s="0" t="inlineStr">
@@ -1503,7 +1503,7 @@
       </c>
       <c r="D3" s="0" t="inlineStr">
         <is>
-          <t>16336721691</t>
+          <t>14660206373</t>
         </is>
       </c>
       <c r="E3" s="0" t="inlineStr"/>
@@ -1524,7 +1524,7 @@
       </c>
       <c r="I3" s="0" t="inlineStr">
         <is>
-          <t>2024-12-18 20:52:16</t>
+          <t>2024-12-26 16:08:28</t>
         </is>
       </c>
       <c r="J3" s="0" t="inlineStr">

--- a/API/CreateData/yizhi.xlsx
+++ b/API/CreateData/yizhi.xlsx
@@ -1342,7 +1342,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W3"/>
+  <dimension ref="A1:W7"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="15" outlineLevelRow="1"/>
   <cols>
     <col width="35.9166666666667" customWidth="1" style="1" min="1" max="1"/>
@@ -1488,7 +1488,7 @@
     <row r="3">
       <c r="A3" s="0" t="inlineStr">
         <is>
-          <t>XG2024122616082814660206373</t>
+          <t>XG2025012017280512845409415</t>
         </is>
       </c>
       <c r="B3" s="0" t="inlineStr">
@@ -1503,7 +1503,7 @@
       </c>
       <c r="D3" s="0" t="inlineStr">
         <is>
-          <t>14660206373</t>
+          <t>12845409415</t>
         </is>
       </c>
       <c r="E3" s="0" t="inlineStr"/>
@@ -1514,17 +1514,17 @@
       </c>
       <c r="G3" s="0" t="inlineStr">
         <is>
-          <t>10025804</t>
+          <t>10025786</t>
         </is>
       </c>
       <c r="H3" s="0" t="inlineStr">
         <is>
-          <t>2.3</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="I3" s="0" t="inlineStr">
         <is>
-          <t>2024-12-26 16:08:28</t>
+          <t>2025-01-20 17:28:05</t>
         </is>
       </c>
       <c r="J3" s="0" t="inlineStr">
@@ -1544,6 +1544,262 @@
       </c>
       <c r="M3" s="0" t="inlineStr"/>
       <c r="O3" s="0" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>XG2025012017280512848197494</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>新贵测试</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>12848197494</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>468078</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>10025786</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>0.04</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2025-01-20 17:28:05</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>第三方售卖</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>1999</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr"/>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>XG2025012017280512848985493</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>新贵测试</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>12848985493</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>468078</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>10025786</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>0.04</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2025-01-20 17:28:05</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>第三方售卖</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>1999</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr"/>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>XG2025012017280515284986483</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>新贵测试</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>15284986483</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>468078</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>10025786</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>0.04</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2025-01-20 17:28:05</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>第三方售卖</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>1999</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr"/>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>XG2025012017280512850532088</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>新贵测试</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>12850532088</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>468078</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>10025786</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>0.04</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>2025-01-20 17:28:05</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>第三方售卖</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>1999</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr"/>
+      <c r="O7" t="inlineStr">
         <is>
           <t>0</t>
         </is>

--- a/API/CreateData/yizhi.xlsx
+++ b/API/CreateData/yizhi.xlsx
@@ -1342,7 +1342,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W7"/>
+  <dimension ref="A1:W3"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="15" outlineLevelRow="1"/>
   <cols>
     <col width="35.9166666666667" customWidth="1" style="1" min="1" max="1"/>
@@ -1488,7 +1488,7 @@
     <row r="3">
       <c r="A3" s="0" t="inlineStr">
         <is>
-          <t>XG2025012017280512845409415</t>
+          <t>XG2025021219282217021914756</t>
         </is>
       </c>
       <c r="B3" s="0" t="inlineStr">
@@ -1503,7 +1503,7 @@
       </c>
       <c r="D3" s="0" t="inlineStr">
         <is>
-          <t>12845409415</t>
+          <t>17021914756</t>
         </is>
       </c>
       <c r="E3" s="0" t="inlineStr"/>
@@ -1524,7 +1524,7 @@
       </c>
       <c r="I3" s="0" t="inlineStr">
         <is>
-          <t>2025-01-20 17:28:05</t>
+          <t>2025-02-12 19:28:22</t>
         </is>
       </c>
       <c r="J3" s="0" t="inlineStr">
@@ -1544,262 +1544,6 @@
       </c>
       <c r="M3" s="0" t="inlineStr"/>
       <c r="O3" s="0" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>XG2025012017280512848197494</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>新贵测试</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>86</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>12848197494</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>468078</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>10025786</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>0.04</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>2025-01-20 17:28:05</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>第三方售卖</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>1999</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr"/>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>XG2025012017280512848985493</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>新贵测试</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>86</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>12848985493</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>468078</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>10025786</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>0.04</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>2025-01-20 17:28:05</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>第三方售卖</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>1999</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr"/>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>XG2025012017280515284986483</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>新贵测试</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>86</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>15284986483</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>468078</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>10025786</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>0.04</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>2025-01-20 17:28:05</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>第三方售卖</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>1999</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr"/>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>XG2025012017280512850532088</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>新贵测试</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>86</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>12850532088</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>468078</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>10025786</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>0.04</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>2025-01-20 17:28:05</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>第三方售卖</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>1999</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr"/>
-      <c r="O7" t="inlineStr">
         <is>
           <t>0</t>
         </is>

--- a/API/CreateData/yizhi.xlsx
+++ b/API/CreateData/yizhi.xlsx
@@ -1488,7 +1488,7 @@
     <row r="3">
       <c r="A3" s="0" t="inlineStr">
         <is>
-          <t>XG2025021219282217021914756</t>
+          <t>XG2025021414103414343076417</t>
         </is>
       </c>
       <c r="B3" s="0" t="inlineStr">
@@ -1503,7 +1503,7 @@
       </c>
       <c r="D3" s="0" t="inlineStr">
         <is>
-          <t>17021914756</t>
+          <t>14343076417</t>
         </is>
       </c>
       <c r="E3" s="0" t="inlineStr"/>
@@ -1514,17 +1514,17 @@
       </c>
       <c r="G3" s="0" t="inlineStr">
         <is>
-          <t>10025786</t>
+          <t>10016649</t>
         </is>
       </c>
       <c r="H3" s="0" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="I3" s="0" t="inlineStr">
         <is>
-          <t>2025-02-12 19:28:22</t>
+          <t>2025-02-14 14:10:34</t>
         </is>
       </c>
       <c r="J3" s="0" t="inlineStr">

--- a/API/CreateData/yizhi.xlsx
+++ b/API/CreateData/yizhi.xlsx
@@ -1488,7 +1488,7 @@
     <row r="3">
       <c r="A3" s="0" t="inlineStr">
         <is>
-          <t>XG2025021414103414343076417</t>
+          <t>XG2025041915314519032487707</t>
         </is>
       </c>
       <c r="B3" s="0" t="inlineStr">
@@ -1503,7 +1503,7 @@
       </c>
       <c r="D3" s="0" t="inlineStr">
         <is>
-          <t>14343076417</t>
+          <t>19032487707</t>
         </is>
       </c>
       <c r="E3" s="0" t="inlineStr"/>
@@ -1514,17 +1514,17 @@
       </c>
       <c r="G3" s="0" t="inlineStr">
         <is>
-          <t>10016649</t>
+          <t>10025786</t>
         </is>
       </c>
       <c r="H3" s="0" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="I3" s="0" t="inlineStr">
         <is>
-          <t>2025-02-14 14:10:34</t>
+          <t>2025-04-19 15:31:45</t>
         </is>
       </c>
       <c r="J3" s="0" t="inlineStr">

--- a/API/CreateData/yizhi.xlsx
+++ b/API/CreateData/yizhi.xlsx
@@ -1488,7 +1488,7 @@
     <row r="3">
       <c r="A3" s="0" t="inlineStr">
         <is>
-          <t>XG2025041915314519032487707</t>
+          <t>XG2025061111015414401041547</t>
         </is>
       </c>
       <c r="B3" s="0" t="inlineStr">
@@ -1503,7 +1503,7 @@
       </c>
       <c r="D3" s="0" t="inlineStr">
         <is>
-          <t>19032487707</t>
+          <t>14401041547</t>
         </is>
       </c>
       <c r="E3" s="0" t="inlineStr"/>
@@ -1514,17 +1514,17 @@
       </c>
       <c r="G3" s="0" t="inlineStr">
         <is>
-          <t>10025786</t>
+          <t>10016747</t>
         </is>
       </c>
       <c r="H3" s="0" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>80</t>
         </is>
       </c>
       <c r="I3" s="0" t="inlineStr">
         <is>
-          <t>2025-04-19 15:31:45</t>
+          <t>2025-06-11 11:01:54</t>
         </is>
       </c>
       <c r="J3" s="0" t="inlineStr">

--- a/API/CreateData/yizhi.xlsx
+++ b/API/CreateData/yizhi.xlsx
@@ -1488,7 +1488,7 @@
     <row r="3">
       <c r="A3" s="0" t="inlineStr">
         <is>
-          <t>XG2025061111015414401041547</t>
+          <t>XG2025070818132717673260026</t>
         </is>
       </c>
       <c r="B3" s="0" t="inlineStr">
@@ -1503,7 +1503,7 @@
       </c>
       <c r="D3" s="0" t="inlineStr">
         <is>
-          <t>14401041547</t>
+          <t>17673260026</t>
         </is>
       </c>
       <c r="E3" s="0" t="inlineStr"/>
@@ -1524,7 +1524,7 @@
       </c>
       <c r="I3" s="0" t="inlineStr">
         <is>
-          <t>2025-06-11 11:01:54</t>
+          <t>2025-07-08 18:13:27</t>
         </is>
       </c>
       <c r="J3" s="0" t="inlineStr">

--- a/API/CreateData/yizhi.xlsx
+++ b/API/CreateData/yizhi.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="22400" windowHeight="10080" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="导入主表" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="获得原因" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="收款渠道" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="支付方式" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="导入主表" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="获得原因" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="收款渠道" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="支付方式" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -1488,7 +1488,7 @@
     <row r="3">
       <c r="A3" s="0" t="inlineStr">
         <is>
-          <t>XG2025070818132717673260026</t>
+          <t>XG2025091115240517665794542</t>
         </is>
       </c>
       <c r="B3" s="0" t="inlineStr">
@@ -1503,7 +1503,7 @@
       </c>
       <c r="D3" s="0" t="inlineStr">
         <is>
-          <t>17673260026</t>
+          <t>17665794542</t>
         </is>
       </c>
       <c r="E3" s="0" t="inlineStr"/>
@@ -1514,17 +1514,17 @@
       </c>
       <c r="G3" s="0" t="inlineStr">
         <is>
-          <t>10016747</t>
+          <t>10026037</t>
         </is>
       </c>
       <c r="H3" s="0" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>51</t>
         </is>
       </c>
       <c r="I3" s="0" t="inlineStr">
         <is>
-          <t>2025-07-08 18:13:27</t>
+          <t>2025-09-11 15:24:05</t>
         </is>
       </c>
       <c r="J3" s="0" t="inlineStr">
@@ -1554,8 +1554,8 @@
     <mergeCell ref="A1:P1"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation sqref="H2" showErrorMessage="1" showInputMessage="1" allowBlank="1" prompt="如果是第三方平台收款，请设置第三方平台收款的金额，并且在豌豆收款金额中填写应该与豌豆结算金额，如果不是请设置为0"/>
-    <dataValidation sqref="I3 K4:L15" showErrorMessage="1" showInputMessage="1" allowBlank="1" type="list">
+    <dataValidation sqref="H2" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" prompt="如果是第三方平台收款，请设置第三方平台收款的金额，并且在豌豆收款金额中填写应该与豌豆结算金额，如果不是请设置为0"/>
+    <dataValidation sqref="I3 K4:L15" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>"微信支付,支付宝支付,银联转账,现金支付,对公转账,库分期"</formula1>
     </dataValidation>
   </dataValidations>
@@ -2183,14 +2183,14 @@
     <row r="265" ht="19.95" customHeight="1" s="1"/>
   </sheetData>
   <mergeCells count="8">
+    <mergeCell ref="A8:A10"/>
+    <mergeCell ref="A17:A18"/>
+    <mergeCell ref="A26:A27"/>
+    <mergeCell ref="A15:A16"/>
     <mergeCell ref="A3:A6"/>
-    <mergeCell ref="A8:A10"/>
+    <mergeCell ref="A23:A24"/>
     <mergeCell ref="A11:A14"/>
-    <mergeCell ref="A15:A16"/>
-    <mergeCell ref="A17:A18"/>
     <mergeCell ref="A19:A22"/>
-    <mergeCell ref="A23:A24"/>
-    <mergeCell ref="A26:A27"/>
   </mergeCells>
   <pageMargins left="0.699305555555556" right="0.699305555555556" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/API/CreateData/yizhi.xlsx
+++ b/API/CreateData/yizhi.xlsx
@@ -1488,7 +1488,7 @@
     <row r="3">
       <c r="A3" s="0" t="inlineStr">
         <is>
-          <t>XG2025091115240517665794542</t>
+          <t>XG2025102418115717117021302</t>
         </is>
       </c>
       <c r="B3" s="0" t="inlineStr">
@@ -1503,7 +1503,7 @@
       </c>
       <c r="D3" s="0" t="inlineStr">
         <is>
-          <t>17665794542</t>
+          <t>17117021302</t>
         </is>
       </c>
       <c r="E3" s="0" t="inlineStr"/>
@@ -1524,7 +1524,7 @@
       </c>
       <c r="I3" s="0" t="inlineStr">
         <is>
-          <t>2025-09-11 15:24:05</t>
+          <t>2025-10-24 18:11:57</t>
         </is>
       </c>
       <c r="J3" s="0" t="inlineStr">

--- a/API/CreateData/yizhi.xlsx
+++ b/API/CreateData/yizhi.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="22400" windowHeight="10080" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="23040" windowHeight="10455" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="导入主表" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="获得原因" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="收款渠道" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="支付方式" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="导入主表" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="获得原因" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="收款渠道" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="支付方式" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -1343,7 +1343,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:W3"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="15" outlineLevelRow="1"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="15.75" outlineLevelRow="2"/>
   <cols>
     <col width="35.9166666666667" customWidth="1" style="1" min="1" max="1"/>
     <col width="14.75" customWidth="1" style="1" min="2" max="2"/>
@@ -1488,7 +1488,7 @@
     <row r="3">
       <c r="A3" s="0" t="inlineStr">
         <is>
-          <t>XG2025102418115717117021302</t>
+          <t>XG2026042709494819880797253</t>
         </is>
       </c>
       <c r="B3" s="0" t="inlineStr">
@@ -1503,7 +1503,7 @@
       </c>
       <c r="D3" s="0" t="inlineStr">
         <is>
-          <t>17117021302</t>
+          <t>19880797253</t>
         </is>
       </c>
       <c r="E3" s="0" t="inlineStr"/>
@@ -1514,17 +1514,17 @@
       </c>
       <c r="G3" s="0" t="inlineStr">
         <is>
-          <t>10026037</t>
+          <t>10026122</t>
         </is>
       </c>
       <c r="H3" s="0" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="I3" s="0" t="inlineStr">
         <is>
-          <t>2025-10-24 18:11:57</t>
+          <t>2026-04-27 09:49:48</t>
         </is>
       </c>
       <c r="J3" s="0" t="inlineStr">
@@ -1572,7 +1572,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A2:D27"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.5"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.85"/>
   <cols>
     <col width="15.4" customWidth="1" style="4" min="1" max="1"/>
     <col width="24.5" customWidth="1" style="4" min="2" max="2"/>
@@ -2203,7 +2203,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:C51"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="15.75"/>
   <cols>
     <col width="11.2" customWidth="1" style="1" min="1" max="1"/>
     <col width="54.6" customWidth="1" style="1" min="2" max="2"/>
